--- a/data/trans_bre/IP1018-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1018-Habitat-trans_bre.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,08</t>
+          <t>-0,68; 1,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 0,0</t>
+          <t>-2,68; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,0</t>
+          <t>-1,66; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 2,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,35</t>
+          <t>-0,47; 0,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,46</t>
+          <t>-0,43; 0,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">

--- a/data/trans_bre/IP1018-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1018-Habitat-trans_bre.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,73</t>
+          <t>-0,69; 2,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 0,0</t>
+          <t>-4,02; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,02</t>
+          <t>-0,64; 1,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 0,0</t>
+          <t>-2,56; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,0</t>
+          <t>-2,1; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,34</t>
+          <t>-0,45; 0,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,45</t>
+          <t>-0,46; 0,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">

--- a/data/trans_bre/IP1018-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1018-Habitat-trans_bre.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,07</t>
+          <t>-0,68; 2,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 0,0</t>
+          <t>-3,61; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,01</t>
+          <t>-0,64; 1,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 0,0</t>
+          <t>-2,42; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 0,0</t>
+          <t>-1,63; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,36</t>
+          <t>-0,49; 0,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,44</t>
+          <t>-0,47; 0,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">

--- a/data/trans_bre/IP1018-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1018-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,129 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,73</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>51,37%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.1760791585527141</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.7347711096626149</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.5137131741259983</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-0,68; 2,08</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-3,61; 0,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-0.6827593361678972</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="n">
+        <v>-3.612620760821989</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.076530274502081</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,64; 1,02</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,71</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+      <c r="C7" s="5" t="n">
+        <v>0.01500112697661454</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.2913966887430314</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.04688155741237759</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,48</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,35</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.6404989016834023</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,42; 0,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,63; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.017413051843872</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="n">
+        <v>1.710942079547507</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +733,185 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,59</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.4807245755373054</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.3527101792933172</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,03</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.417403150238838</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="n">
+        <v>-1.634965244917478</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.5884283897078664</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="n">
+        <v>2.027261041942938</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,06</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-24,2%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>15,12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,49; 0,35</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,47; 0,46</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.06439072498338003</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.03401625217915086</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0.2420011979525785</v>
+      </c>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="n">
+        <v>0.1511839456474231</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.4945268868845481</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="n">
+        <v>-0.4740622961857386</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.3451884033792699</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="n">
+        <v>0.4605091489647202</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +920,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
